--- a/data/google_news_dedup_audit_30_0426_UTC.xlsx
+++ b/data/google_news_dedup_audit_30_0426_UTC.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -445,10 +445,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C2" t="n">
         <v>0.9718902111053467</v>
@@ -466,7 +466,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B3" t="n">
         <v>6</v>
@@ -487,55 +487,55 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B4" t="n">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7649838328361511</v>
+        <v>0.8594973683357239</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Corteo per Sergio Ramelli a Milano tra fiaccole, saluti romani e insulti dai balconi: il video del "presente" - Virgilio</t>
+          <t>Yoga in luftiger Höhe: Polizei beendet Video-Dreh auf Ingolstädter Kirchturm - Augsburger Allgemeine</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Saluti romani al corteo in ricordo di Sergio Ramelli a Milano - il Nord Est</t>
+          <t>Polizei stoppt Yoga-Video-Dreharbeiten auf Kirchturm-Gerüst in Ingolstadt - Pfaffenhofen Today</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B5" t="n">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="C5" t="n">
-        <v>0.6877677440643311</v>
+        <v>0.838911771774292</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Corteo per Sergio Ramelli a Milano tra fiaccole, saluti romani e insulti dai balconi: il video del "presente" - Virgilio</t>
+          <t>Yoga in luftiger Höhe: Polizei beendet Video-Dreh auf Ingolstädter Kirchturm - Augsburger Allgemeine</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Saluti romani al corteo per Ramelli a Milano - La Stampa</t>
+          <t>Session in luftiger Höhe: Mann dreht Yoga-Video auf Kirchturm-Gerüst - Nordbayern</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="B6" t="n">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7630565166473389</v>
+        <v>0.7649838328361511</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -544,19 +544,19 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Saluti romani al corteo in ricordo di Sergio Ramelli a Milano - Quotidiano Nazionale</t>
+          <t>Saluti romani al corteo in ricordo di Sergio Ramelli a Milano - il Nord Est</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="B7" t="n">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="C7" t="n">
-        <v>0.79599928855896</v>
+        <v>0.7630565166473389</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -565,68 +565,26 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Milano, corteo in ricordo di Sergio Ramelli: saluti romani alla chiamata del "presente" - La Stampa</t>
+          <t>Saluti romani al corteo in ricordo di Sergio Ramelli a Milano - Quotidiano Nazionale</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="B8" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="C8" t="n">
-        <v>0.6390817165374756</v>
+        <v>0.7274889945983887</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Corteo per Sergio Ramelli a Milano tra fiaccole, saluti romani e insulti dai balconi: il video del "presente" - Virgilio</t>
+          <t>Primo maggio 2026, cosa fare a Milano? Corteo, sagre, eventi da non perdere - Mentelocale</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
-        <is>
-          <t>Milano, commemorazione di Sergio Ramelli: corteo dell'ultradestra e aggressione nella notte - Il Gazzettino Metropolitano</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>43</v>
-      </c>
-      <c r="B9" t="n">
-        <v>52</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.9051393270492554</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Corteo per Sergio Ramelli a Milano tra fiaccole, saluti romani e insulti dai balconi: il video del "presente" - Virgilio</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Corteo per Sergio Ramelli a Milano tra fiaccole saluti romani e insulti dai balconi | il video del presente - Zazoom Social News</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>44</v>
-      </c>
-      <c r="B10" t="n">
-        <v>51</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0.7274889945983887</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Primo maggio 2026, cosa fare a Milano? Corteo, sagre, eventi da non perdere - Mentelocale</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
         <is>
           <t>Festa dei Lavoratori. Cgil, Cisl, Uil danno appuntamento a Milano per il tradizionale corteo che il Primo Maggio - mi-lorenteggio.com</t>
         </is>
